--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -1,47 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0ae640eb478e76d3/Desktop/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{AD3CDDCB-F30A-4E09-A0AC-B3899C5797E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{884EA358-7B63-484F-B02C-D612BB5D0AC3}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Jobs" sheetId="1" r:id="rId1"/>
+    <sheet name="Candidates" sheetId="2" r:id="rId2"/>
+    <sheet name="Meta" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -67,21 +67,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -96,44 +88,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -161,31 +153,14 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -213,23 +188,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -241,136 +199,180 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="100000"/>
                 <a:shade val="100000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
     <a:lnDef>
       <a:spPr/>
       <a:bodyPr/>
@@ -392,19 +394,177 @@
     </a:lnDef>
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{062ECD69-37E5-4B46-8863-DB67421A9FE2}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>title</v>
+      </c>
+      <c r="C1" t="str">
+        <v>dept</v>
+      </c>
+      <c r="D1" t="str">
+        <v>exp</v>
+      </c>
+      <c r="E1" t="str">
+        <v>salary</v>
+      </c>
+      <c r="F1" t="str">
+        <v>responsibilities</v>
+      </c>
+      <c r="G1" t="str">
+        <v>skills</v>
+      </c>
+      <c r="H1" t="str">
+        <v>nice</v>
+      </c>
+      <c r="I1" t="str">
+        <v>notes</v>
+      </c>
+      <c r="J1" t="str">
+        <v>createdAt</v>
+      </c>
+    </row>
+    <row r="2" xml:space="preserve">
+      <c r="A2" t="str">
+        <v>JOB-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>AI Governance Consultant</v>
+      </c>
+      <c r="C2" t="str">
+        <v>AI Risk &amp; Governance / Advisory</v>
+      </c>
+      <c r="D2" t="str">
+        <v>5+ years</v>
+      </c>
+      <c r="E2" t="str">
+        <v>₹25–40 LPA or equivalent</v>
+      </c>
+      <c r="F2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Lead client-facing AI governance engagements (S1 &amp; S2)
+Conduct AI system inventories and governance assessments
+Facilitate AI risk classification workshops with stakeholders
+Design and implement AI governance frameworks
+Advise clients on responsible AI policies, controls, and operating models
+Collaborate with cross-functional client teams across legal, compliance, product, and engineering</v>
+      </c>
+      <c r="G2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Deep expertise in NIST AI RMF and ISO/IEC 42001
+Strong understanding of AI governance, AI risk management, and compliance frameworks
+Experience running governance workshops and stakeholder sessions
+Knowledge of AI lifecycle management and model governance
+Excellent communication and client management skills
+Ability to translate regulatory requirements into operational processes</v>
+      </c>
+      <c r="H2" t="str" xml:space="preserve">
+        <v xml:space="preserve">Experience with enterprise AI deployments
+Familiarity with EU AI Act or global AI regulations
+Background in consulting or advisory services
+Certifications in risk, security, or governance frameworks</v>
+      </c>
+      <c r="I2" t="str">
+        <v>This is a highly client-facing role requiring strong facilitation and strategic communication skills. Candidate should be comfortable leading workshops, engaging executive stakeholders, and shaping governance programs for enterprise AI adoption. Experience handling complex governance initiatives across multiple teams is preferred.</v>
+      </c>
+      <c r="J2" t="str">
+        <v>2026-05-21T21:25:08.345Z</v>
+      </c>
+    </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>JOB-002</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Client Engagement Lead</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Client Success / Advisory Operations</v>
+      </c>
+      <c r="D3" t="str">
+        <v>4+ years</v>
+      </c>
+      <c r="E3" t="str">
+        <v>₹18–30 LPA or equivalent</v>
+      </c>
+      <c r="F3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Own client relationships from initial onboarding to final deliverable
+Manage engagement timelines, milestones, and communication
+Coordinate between internal advisors and client stakeholders
+Ensure engagements are delivered on scope, quality, and timelines
+Track action items, risks, and dependencies across projects
+Maintain high client satisfaction and engagement quality standards
+Support proposal follow-ups, reporting, and engagement documentation</v>
+      </c>
+      <c r="G3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Strong client relationship and stakeholder management skills
+Excellent project coordination and communication abilities
+Experience managing consulting, advisory, or professional service engagements
+Ability to manage multiple concurrent projects and deadlines
+Strong organizational and operational execution skills
+Comfortable working with cross-functional teams and senior leadership
+Proficiency with project management and collaboration tools</v>
+      </c>
+      <c r="H3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Experience in AI, governance, compliance, or technology consulting environments
+Familiarity with enterprise client engagement workflows
+Background in customer success, consulting operations, or program management
+Experience preparing executive-level reports and presentations</v>
+      </c>
+      <c r="I3" t="str">
+        <v>This role is critical to ensuring seamless client delivery and long-term relationship success. The ideal candidate should be proactive, detail-oriented, and highly organized, with the ability to manage complex stakeholder environments while maintaining a polished client experience throughout every engagement.</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2026-05-21T21:27:03.945Z</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A2"/>
   <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>jobCounter</v>
+      </c>
+      <c r="B1" t="str">
+        <v>candCounter</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B2"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -525,9 +525,57 @@
         <v>2026-05-21T21:27:03.945Z</v>
       </c>
     </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
+        <v>JOB-003</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Regulatory Policy Specialist</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Policy Research / AI Governance</v>
+      </c>
+      <c r="D4" t="str">
+        <v>4+ years</v>
+      </c>
+      <c r="E4" t="str">
+        <v>₹20–35 LPA or equivalent</v>
+      </c>
+      <c r="F4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Monitor global AI regulatory and standards developments
+Track updates related to the EU AI Act, NIST AI RMF, and ISO/IEC 42001
+Analyze sector-specific AI guidance, policies, and compliance expectations
+Translate regulatory developments into actionable business implications for clients
+Prepare policy briefings, risk summaries, and regulatory update reports
+Support internal advisory teams with governance and compliance insights
+Maintain regulatory intelligence repositories and tracking systems</v>
+      </c>
+      <c r="G4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Strong understanding of AI governance and regulatory frameworks
+Deep familiarity with NIST AI RMF, ISO/IEC 42001, and EU AI Act requirements
+Ability to interpret legal, regulatory, and standards documentation
+Excellent research, analysis, and written communication skills
+Experience translating policy language into operational guidance
+Strong attention to detail and ability to track evolving regulations across jurisdictions</v>
+      </c>
+      <c r="H4" t="str" xml:space="preserve">
+        <v xml:space="preserve">Background in technology policy, compliance, risk, or governance consulting
+Familiarity with emerging global AI regulations and standards bodies
+Experience working with enterprise compliance or legal teams
+Understanding of AI lifecycle management and responsible AI practices</v>
+      </c>
+      <c r="I4" t="str" xml:space="preserve">
+        <v xml:space="preserve">This role is ideal for someone who enjoys staying ahead of fast-moving regulatory developments and turning complex policy changes into practical guidance for organizations. The candidate should be highly analytical, research-driven, and capable of communicating nuanced regulatory insights clearly to both technical and non-technical stakeholders.
+CORE FRAMEWORKS &amp; STANDARDS
+NIST AI RMF · ISO/IEC 42001 · EU AI Act</v>
+      </c>
+      <c r="J4" t="str">
+        <v>2026-05-21T21:29:12.081Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -556,7 +604,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2">
         <v>0</v>

--- a/DATA.xlsx
+++ b/DATA.xlsx
@@ -582,10 +582,141 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetData/>
+  <dimension ref="A1:U2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>name</v>
+      </c>
+      <c r="C1" t="str">
+        <v>role</v>
+      </c>
+      <c r="D1" t="str">
+        <v>dept</v>
+      </c>
+      <c r="E1" t="str">
+        <v>email</v>
+      </c>
+      <c r="F1" t="str">
+        <v>intType</v>
+      </c>
+      <c r="G1" t="str">
+        <v>date</v>
+      </c>
+      <c r="H1" t="str">
+        <v>jobId</v>
+      </c>
+      <c r="I1" t="str">
+        <v>jobTitle</v>
+      </c>
+      <c r="J1" t="str">
+        <v>recommendation</v>
+      </c>
+      <c r="K1" t="str">
+        <v>avgScore</v>
+      </c>
+      <c r="L1" t="str">
+        <v>ratedCount</v>
+      </c>
+      <c r="M1" t="str">
+        <v>overallNotes</v>
+      </c>
+      <c r="N1" t="str">
+        <v>recReason</v>
+      </c>
+      <c r="O1" t="str">
+        <v>submittedAt</v>
+      </c>
+      <c r="P1" t="str">
+        <v>score_tech</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>score_comm</v>
+      </c>
+      <c r="R1" t="str">
+        <v>score_prob</v>
+      </c>
+      <c r="S1" t="str">
+        <v>score_cult</v>
+      </c>
+      <c r="T1" t="str">
+        <v>score_lead</v>
+      </c>
+      <c r="U1" t="str">
+        <v>score_grow</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>CAND-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Piyal Gupta</v>
+      </c>
+      <c r="C2" t="str">
+        <v>CEO</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Corporate Functions</v>
+      </c>
+      <c r="E2" t="str">
+        <v>piyal@outlook.com</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Final Round</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2026-05-21</v>
+      </c>
+      <c r="H2" t="str">
+        <v>—</v>
+      </c>
+      <c r="I2" t="str">
+        <v>CEO</v>
+      </c>
+      <c r="J2" t="str">
+        <v>hire</v>
+      </c>
+      <c r="K2" t="str">
+        <v>4.5</v>
+      </c>
+      <c r="L2">
+        <v>6</v>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v>2026-05-21T21:32:32.281Z</v>
+      </c>
+      <c r="P2">
+        <v>4</v>
+      </c>
+      <c r="Q2">
+        <v>4</v>
+      </c>
+      <c r="R2">
+        <v>4</v>
+      </c>
+      <c r="S2">
+        <v>5</v>
+      </c>
+      <c r="T2">
+        <v>5</v>
+      </c>
+      <c r="U2">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U2"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -607,7 +738,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
